--- a/templates/container_6m.xlsx
+++ b/templates/container_6m.xlsx
@@ -1,31 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Joris\gb-etats-des-lieux\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Joris\gb-etats-des-lieux\modeles_reels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C4B41A6-0644-40BB-9DF7-996D656BB4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A909F27-3105-48AF-A809-81E3AC10376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12660" xr2:uid="{E03D6491-6D0B-4108-A9FB-DDD5F01BDFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="CONTAINER 6m (perspectives)" sheetId="10" r:id="rId1"/>
+    <sheet name="CONTAINER 6m" sheetId="8" r:id="rId2"/>
+    <sheet name="CONTAINER 3m 10pieds" sheetId="11" r:id="rId3"/>
+    <sheet name="CONTAINER 3m 8pieds" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="101716"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="37">
   <si>
     <t>ETAT INTERIEUR</t>
   </si>
   <si>
     <t>ETAT EXTERIEUR</t>
+  </si>
+  <si>
+    <t>Longpan AR</t>
+  </si>
+  <si>
+    <t>Longpan AV</t>
   </si>
   <si>
     <t>Légende</t>
@@ -53,6 +73,12 @@
   </si>
   <si>
     <t>Signature précédée mention "bon pour accord"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          Pignon D</t>
+  </si>
+  <si>
+    <t>Pignon G</t>
   </si>
   <si>
     <t>Sol</t>
@@ -85,6 +111,9 @@
     <t>CADENAS N°</t>
   </si>
   <si>
+    <t>CLIENT :</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHANTIER : </t>
   </si>
   <si>
@@ -100,7 +129,13 @@
     <t>CHENEAUX NETTOYES   OUI    NON</t>
   </si>
   <si>
+    <t>TAILLE : 3M x 2,50M - 10'</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLIENT : </t>
+  </si>
+  <si>
+    <t>Container : ………………</t>
   </si>
   <si>
     <t>15m² - 6m x 2,50m</t>
@@ -108,12 +143,15 @@
   <si>
     <t>EN COULEUR LES REMARQUES DE RETOUR</t>
   </si>
+  <si>
+    <t>TAILLE : 2,43m x 2,20m - 8'</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -162,6 +200,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -323,45 +367,187 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -374,141 +560,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,6 +831,1110 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8271" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A6606BE-E437-80B8-7195-6785072E410D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2257425"/>
+          <a:ext cx="2533650" cy="1257300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8272" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B008A760-4A1D-3601-9EAD-B53E00959D2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3057525" y="2228850"/>
+          <a:ext cx="2495550" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F7D5D3-8F31-7A4B-825D-6F11E8C6934B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3248025" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>300990</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>198127</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCCA69E7-49BE-5444-35DA-677F3D47D926}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8275" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4489E0F2-F86F-8A8C-5763-1EC07993D543}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13333" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14D7D59A-7EEB-93AF-0CB3-83197834F597}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="781050" y="2266950"/>
+          <a:ext cx="1457325" cy="1257300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13334" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0504F47D-10DC-FD5B-712B-4590C0591A2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3810000" y="2228850"/>
+          <a:ext cx="1419225" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1068166-7E8A-9059-BA5C-B5D048A98231}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3143250" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>300990</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>198127</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{124CBB1C-FF6E-D4A0-909D-603D56CABEF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="300990" y="161925"/>
+          <a:ext cx="659137" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13337" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0C411C0-D243-BB3C-140B-5293E1D2B66B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11315" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{473CD762-BE30-61B3-0AD2-A20C9F05FD10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="781050" y="2266950"/>
+          <a:ext cx="1457325" cy="1257300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11316" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9538DFC-120D-0518-0F86-0670B87CD43C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3810000" y="2228850"/>
+          <a:ext cx="1419225" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DDA4D8B-82E6-5774-3D1F-1B9B52FB0AF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3143250" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>300990</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>198127</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8FFCD28-2062-20A4-1E14-17BA3356EDCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11319" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC8738C2-7C8B-112C-D7B0-1C8C5EF5CFCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1150,418 +2313,457 @@
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="11" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="63" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="64" t="s">
+      <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="F11" s="13" t="s">
-        <v>28</v>
+      <c r="A11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="F11" s="18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="8"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="10"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="8"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="10"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="8"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="10"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="60" t="s">
+      <c r="A24" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="61"/>
-      <c r="G24" s="60" t="s">
+      <c r="B24" s="30"/>
+      <c r="C24" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="61"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="32"/>
+      <c r="G24" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
+      <c r="C25" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="34"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="34"/>
+      <c r="H25" s="35"/>
     </row>
     <row r="26" spans="1:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="37"/>
+      <c r="C26" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="39"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+    </row>
+    <row r="27" spans="1:8" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+    </row>
+    <row r="28" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="34"/>
+      <c r="H30" s="35"/>
+    </row>
+    <row r="31" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="45"/>
+      <c r="C31" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="22" t="s">
+      <c r="G31" s="51"/>
+      <c r="H31" s="52"/>
+    </row>
+    <row r="32" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="46"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="54"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+    </row>
+    <row r="33" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="48"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="57"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="57"/>
+      <c r="H33" s="58"/>
+    </row>
+    <row r="34" spans="1:8" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="60"/>
+      <c r="C34" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+    </row>
+    <row r="35" spans="1:8" s="14" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+    </row>
+    <row r="36" spans="1:8" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-    </row>
-    <row r="27" spans="1:8" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
-    </row>
-    <row r="28" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
-    </row>
-    <row r="30" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="34"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
-    </row>
-    <row r="31" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="46"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="46"/>
-      <c r="H31" s="47"/>
-    </row>
-    <row r="32" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="49"/>
-      <c r="H32" s="50"/>
-    </row>
-    <row r="33" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="43"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="52"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="52"/>
-      <c r="H33" s="53"/>
-    </row>
-    <row r="34" spans="1:8" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="B36" s="65"/>
+      <c r="C36" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="39"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
+    </row>
+    <row r="37" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="67"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="69"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="24"/>
-    </row>
-    <row r="35" spans="1:8" s="11" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="27"/>
-    </row>
-    <row r="36" spans="1:8" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="23"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="24"/>
-    </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="17"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
+      <c r="A40" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
+      <c r="A42" s="71"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E2:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A31:B33"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="F27:H27"/>
@@ -1572,39 +2774,1481 @@
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:H24"/>
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:H8"/>
+  </mergeCells>
+  <pageMargins left="0.16" right="0.15" top="0.25" bottom="0.22" header="0.17" footer="0.15"/>
+  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E47D6E7-ACD5-4099-B861-3F90AC6BF57C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="F11" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="10"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="10"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="10"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="32"/>
+      <c r="G22" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="34"/>
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+    </row>
+    <row r="25" spans="1:8" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+    </row>
+    <row r="26" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
+    </row>
+    <row r="29" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="46"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="54"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+    </row>
+    <row r="31" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="57"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="57"/>
+      <c r="H31" s="58"/>
+    </row>
+    <row r="32" spans="1:8" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="60"/>
+      <c r="C32" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+    </row>
+    <row r="33" spans="1:8" s="14" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="63"/>
+    </row>
+    <row r="34" spans="1:8" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="65"/>
+      <c r="C34" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+    </row>
+    <row r="35" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="67"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="69"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="71"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="F25:H25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A29:B31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="A31:B33"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="F33:H33"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:H38"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.16" right="0.15" top="0.25" bottom="0.22" header="0.17" footer="0.15"/>
+  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DF4F08-C123-4CCC-975E-87868917AE77}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="10"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="10"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="10"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="32"/>
+      <c r="G22" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="34"/>
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+    </row>
+    <row r="25" spans="1:8" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+    </row>
+    <row r="26" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
+    </row>
+    <row r="29" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="46"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="54"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+    </row>
+    <row r="31" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="57"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="57"/>
+      <c r="H31" s="58"/>
+    </row>
+    <row r="32" spans="1:8" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="60"/>
+      <c r="C32" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+    </row>
+    <row r="33" spans="1:8" s="14" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="63"/>
+    </row>
+    <row r="34" spans="1:8" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="65"/>
+      <c r="C34" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+    </row>
+    <row r="35" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="67"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="69"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="71"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A29:B31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="F34:H34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:H36"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="E40:H40"/>
   </mergeCells>
   <pageMargins left="0.16" right="0.15" top="0.25" bottom="0.22" header="0.17" footer="0.15"/>
-  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BDBCDD9-0393-49E0-9374-5D027397BE17}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="10"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="10"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="10"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="32"/>
+      <c r="G22" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="34"/>
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+    </row>
+    <row r="25" spans="1:8" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+    </row>
+    <row r="26" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
+    </row>
+    <row r="29" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="46"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="54"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="54"/>
+      <c r="H30" s="55"/>
+    </row>
+    <row r="31" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="57"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="57"/>
+      <c r="H31" s="58"/>
+    </row>
+    <row r="32" spans="1:8" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="60"/>
+      <c r="C32" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+    </row>
+    <row r="33" spans="1:8" s="14" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="63"/>
+    </row>
+    <row r="34" spans="1:8" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="65"/>
+      <c r="C34" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+    </row>
+    <row r="35" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="67"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="69"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="71"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A29:B31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:H40"/>
+  </mergeCells>
+  <pageMargins left="0.16" right="0.15" top="0.25" bottom="0.22" header="0.17" footer="0.15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
